--- a/PYTEST DATADRIVEN USING EXCEL/ExcelFiles/logindata.xlsx
+++ b/PYTEST DATADRIVEN USING EXCEL/ExcelFiles/logindata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Python Selenium\PYTEST DATADRIVEN USING EXCEL\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20E0F67-A96A-4BB9-9083-AE5B3C63AF5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA449250-705F-4E83-BDF6-2B6819420623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="login" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
   <si>
     <t>username</t>
   </si>
@@ -34,9 +34,6 @@
   </si>
   <si>
     <t>vithyamurugesan</t>
-  </si>
-  <si>
-    <t>vithy</t>
   </si>
 </sst>
 </file>
@@ -378,7 +375,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3">
         <v>12</v>
